--- a/files/九龙-长沙湾-喜．扬.xlsx
+++ b/files/九龙-长沙湾-喜．扬.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="喜．扬 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="喜．扬" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,10 +237,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -4508,135 +4546,135 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>喜．扬 - 喜．扬 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>喜．扬 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>83 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>81 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 429呎 (2房)
-$1,115万
+$1115万
 $26,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 398呎 (2房)
 招标单位
@@ -4644,17 +4682,17 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr"/>
+      <c r="E5" s="22" t="inlineStr"/>
+      <c r="F5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 296呎 (1房)
 $649万
@@ -4662,7 +4700,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 323呎 (1房)
 $641万
@@ -4670,7 +4708,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 305呎 (1房)
 $616万
@@ -4678,8 +4716,8 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
 $464万
@@ -4688,13 +4726,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 296呎 (1房)
 $586万
@@ -4702,7 +4740,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 323呎 (1房)
 $628万
@@ -4710,7 +4748,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 305呎 (1房)
 $604万
@@ -4718,8 +4756,8 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
 $455万
@@ -4728,13 +4766,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 296呎 (1房)
 $558万
@@ -4742,7 +4780,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 323呎 (1房)
 $619万
@@ -4750,7 +4788,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 305呎 (1房)
 $595万
@@ -4758,8 +4796,8 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
 $453万
@@ -4768,13 +4806,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 296呎 (1房)
 $553万
@@ -4782,7 +4820,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 323呎 (1房)
 $598万
@@ -4790,7 +4828,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 305呎 (1房)
 $557万
@@ -4798,8 +4836,8 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
 $449万
@@ -4808,13 +4846,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 296呎 (1房)
 $555万
@@ -4822,7 +4860,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 206呎 (开放式)
 $376万
@@ -4830,7 +4868,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $396万
@@ -4838,7 +4876,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $418万
@@ -4846,7 +4884,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
 $446万
@@ -4855,13 +4893,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 296呎 (1房)
 $550万
@@ -4869,7 +4907,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 206呎 (开放式)
 $373万
@@ -4877,7 +4915,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $393万
@@ -4885,7 +4923,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $424万
@@ -4893,7 +4931,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
 $433万
@@ -4902,13 +4940,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 296呎 (1房)
 $566万
@@ -4916,7 +4954,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 206呎 (开放式)
 $362万
@@ -4924,7 +4962,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $382万
@@ -4932,7 +4970,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $408万
@@ -4940,7 +4978,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
 $426万
@@ -4949,13 +4987,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 296呎 (1房)
 $553万
@@ -4963,7 +5001,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 206呎 (开放式)
 $358万
@@ -4971,7 +5009,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $471万
@@ -4979,7 +5017,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $398万
@@ -4987,7 +5025,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
 $420万
@@ -4996,13 +5034,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 273呎 (1房)
 $526万
@@ -5010,7 +5048,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 206呎 (开放式)
 $355万
@@ -5018,7 +5056,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $377万
@@ -5026,7 +5064,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $440万
@@ -5034,7 +5072,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
 $443万
@@ -5043,13 +5081,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 391呎 (2房)
 $650万
@@ -5057,7 +5095,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 203呎 (开放式)
 $354万
@@ -5065,7 +5103,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $380万
@@ -5073,7 +5111,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $393万
@@ -5081,7 +5119,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 297呎 (1房)
 $524万
@@ -5090,13 +5128,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 391呎 (2房)
 $680万
@@ -5104,7 +5142,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 203呎 (开放式)
 $350万
@@ -5112,7 +5150,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $460万
@@ -5120,7 +5158,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $388万
@@ -5128,7 +5166,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 297呎 (1房)
 $622万
@@ -5137,13 +5175,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 391呎 (2房)
 $598万
@@ -5151,7 +5189,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 203呎 (开放式)
 $347万
@@ -5159,7 +5197,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $368万
@@ -5167,7 +5205,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $383万
@@ -5175,7 +5213,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 297呎 (1房)
 $604万
@@ -5184,13 +5222,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 391呎 (2房)
 $769万
@@ -5198,7 +5236,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 203呎 (开放式)
 $349万
@@ -5206,7 +5244,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $366万
@@ -5214,7 +5252,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $378万
@@ -5222,7 +5260,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 297呎 (1房)
 $484万
@@ -5231,13 +5269,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 391呎 (2房)
 $650万
@@ -5245,7 +5283,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 204呎 (开放式)
 $424万
@@ -5253,7 +5291,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $451万
@@ -5261,7 +5299,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $371万
@@ -5269,7 +5307,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 297呎 (1房)
 $491万
@@ -5278,13 +5316,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 391呎 (2房)
 $758万
@@ -5292,7 +5330,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 203呎 (开放式)
 $324万
@@ -5300,7 +5338,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $447万
@@ -5308,7 +5346,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $367万
@@ -5316,7 +5354,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 297呎 (1房)
 $478万
@@ -5325,13 +5363,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 391呎 (2房)
 $747万
@@ -5339,7 +5377,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 204呎 (开放式)
 $418万
@@ -5347,7 +5385,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 216呎 (开放式)
 $443万
@@ -5355,7 +5393,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 228呎 (开放式)
 $369万
@@ -5363,7 +5401,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 297呎 (1房)
 $475万
@@ -5372,13 +5410,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 368呎 (开放式)
 $807万
@@ -5386,7 +5424,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 183呎 (开放式)
 $396万
@@ -5394,7 +5432,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 195呎 (开放式)
 $422万
@@ -5402,7 +5440,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 207呎 (开放式)
 $361万
@@ -5410,7 +5448,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 274呎 (开放式)
 $493万
